--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23925" windowHeight="11070"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="26070" windowHeight="11745"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,115 +16,115 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <x:si>
+    <x:t>Harvest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropCountRange</x:t>
+  </x:si>
+  <x:si>
     <x:t>FieldObjectType</x:t>
   </x:si>
   <x:si>
     <x:t>harv_carrot_1</x:t>
   </x:si>
   <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
     <x:t>harv_potate_1</x:t>
   </x:si>
   <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Potato_1</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropCountRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Carrot_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>옥수수</x:t>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>필드 채집용 옥수수</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
+    <x:t>필드 채집용 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Harvest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -434,7 +434,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -517,7 +516,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -552,7 +550,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -597,7 +594,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -641,7 +637,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -726,7 +721,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -747,7 +741,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -778,7 +771,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1494,92 +1486,92 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="18" t="s">
-        <x:v>33</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="s">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="15"/>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>31</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
@@ -1598,26 +1590,26 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="21" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F5" s="21" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="F5" s="21" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1632,26 +1624,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F6" s="26" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="E6" s="20" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F6" s="26" t="s">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1666,24 +1658,24 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="27" t="s">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D7" s="7"/>
       <x:c r="E7" s="20" t="s">
-        <x:v>31</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F7" s="26" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="20"/>
       <x:c r="H7" s="26" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="5"/>
